--- a/data/metadata_raw/births_total.xlsx
+++ b/data/metadata_raw/births_total.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="1235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="1237">
   <si>
     <t>Code</t>
   </si>
@@ -77,6 +77,9 @@
     <t>2024</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>1700</t>
   </si>
   <si>
@@ -2852,6 +2855,9 @@
     <t>Бухоро тумани</t>
   </si>
   <si>
+    <t>Вобкент тумани</t>
+  </si>
+  <si>
     <t>Ғиждувон тумани</t>
   </si>
   <si>
@@ -3596,7 +3602,7 @@
     <t>2022-06-01</t>
   </si>
   <si>
-    <t>2022-08-04</t>
+    <t>2026-04-20</t>
   </si>
   <si>
     <t>2.01.01.0001</t>
@@ -4077,10 +4083,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T222"/>
+  <dimension ref="A1:U222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4141,22 +4147,25 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F2">
         <v>634810</v>
@@ -4203,22 +4212,25 @@
       <c r="T2">
         <v>926422</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="U2">
+        <v>879599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F3">
         <v>37942</v>
@@ -4265,22 +4277,25 @@
       <c r="T3">
         <v>41641</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="U3">
+        <v>39277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F4">
         <v>6220</v>
@@ -4327,22 +4342,25 @@
       <c r="T4">
         <v>6721</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="U4">
+        <v>6065</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E5" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F5">
         <v>3576</v>
@@ -4389,22 +4407,25 @@
       <c r="T5">
         <v>4880</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="U5">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E6" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F6">
         <v>3918</v>
@@ -4451,22 +4472,25 @@
       <c r="T6">
         <v>4986</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="U6">
+        <v>4933</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D7" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E7" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -4513,22 +4537,25 @@
       <c r="T7">
         <v>370</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="U7">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E8" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F8">
         <v>1142</v>
@@ -4575,22 +4602,25 @@
       <c r="T8">
         <v>974</v>
       </c>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="U8">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F9">
         <v>1873</v>
@@ -4637,22 +4667,25 @@
       <c r="T9">
         <v>1452</v>
       </c>
-    </row>
-    <row r="10" spans="1:20">
+      <c r="U9">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D10" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E10" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F10">
         <v>2825</v>
@@ -4699,22 +4732,25 @@
       <c r="T10">
         <v>2629</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="U10">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D11" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E11" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F11">
         <v>953</v>
@@ -4761,22 +4797,25 @@
       <c r="T11">
         <v>1079</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="U11">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D12" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E12" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F12">
         <v>637</v>
@@ -4823,22 +4862,25 @@
       <c r="T12">
         <v>644</v>
       </c>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="U12">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D13" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E13" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F13">
         <v>1060</v>
@@ -4885,22 +4927,25 @@
       <c r="T13">
         <v>1212</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="U13">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D14" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E14" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F14">
         <v>1038</v>
@@ -4947,22 +4992,25 @@
       <c r="T14">
         <v>1344</v>
       </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="U14">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C15" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D15" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E15" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F15">
         <v>943</v>
@@ -5009,22 +5057,25 @@
       <c r="T15">
         <v>644</v>
       </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="U15">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C16" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D16" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E16" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="F16">
         <v>3997</v>
@@ -5071,22 +5122,25 @@
       <c r="T16">
         <v>5012</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
+      <c r="U16">
+        <v>5042</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C17" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E17" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F17">
         <v>3163</v>
@@ -5133,22 +5187,25 @@
       <c r="T17">
         <v>2628</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
+      <c r="U17">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C18" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D18" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E18" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F18">
         <v>2489</v>
@@ -5195,22 +5252,25 @@
       <c r="T18">
         <v>2274</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="U18">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C19" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D19" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E19" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F19">
         <v>991</v>
@@ -5257,22 +5317,25 @@
       <c r="T19">
         <v>927</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="U19">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C20" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D20" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E20" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F20">
         <v>3117</v>
@@ -5319,22 +5382,25 @@
       <c r="T20">
         <v>3865</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="U20">
+        <v>3998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C21" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D21" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E21" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F21">
         <v>59953</v>
@@ -5381,22 +5447,25 @@
       <c r="T21">
         <v>86305</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
+      <c r="U21">
+        <v>79672</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D22" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E22" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F22">
         <v>8369</v>
@@ -5443,22 +5512,25 @@
       <c r="T22">
         <v>15694</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
+      <c r="U22">
+        <v>14581</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D23" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E23" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F23">
         <v>761</v>
@@ -5505,22 +5577,25 @@
       <c r="T23">
         <v>811</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
+      <c r="U23">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C24" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D24" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E24" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F24">
         <v>3368</v>
@@ -5567,22 +5642,25 @@
       <c r="T24">
         <v>3120</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
+      <c r="U24">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C25" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D25" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E25" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F25">
         <v>4941</v>
@@ -5629,22 +5707,25 @@
       <c r="T25">
         <v>7673</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
+      <c r="U25">
+        <v>7251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D26" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E26" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F26">
         <v>3725</v>
@@ -5691,22 +5772,25 @@
       <c r="T26">
         <v>5594</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
+      <c r="U26">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C27" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D27" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E27" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F27">
         <v>1400</v>
@@ -5753,22 +5837,25 @@
       <c r="T27">
         <v>2241</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
+      <c r="U27">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D28" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E28" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F28">
         <v>2520</v>
@@ -5815,22 +5902,25 @@
       <c r="T28">
         <v>3832</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
+      <c r="U28">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D29" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E29" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F29">
         <v>3508</v>
@@ -5877,22 +5967,25 @@
       <c r="T29">
         <v>4637</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
+      <c r="U29">
+        <v>4336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D30" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E30" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F30">
         <v>4691</v>
@@ -5939,22 +6032,25 @@
       <c r="T30">
         <v>6486</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
+      <c r="U30">
+        <v>6155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C31" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D31" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E31" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F31">
         <v>1169</v>
@@ -6001,22 +6097,25 @@
       <c r="T31">
         <v>940</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
+      <c r="U31">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C32" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D32" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E32" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F32">
         <v>4229</v>
@@ -6063,22 +6162,25 @@
       <c r="T32">
         <v>5257</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
+      <c r="U32">
+        <v>4924</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C33" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D33" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E33" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F33">
         <v>6093</v>
@@ -6125,22 +6227,25 @@
       <c r="T33">
         <v>9157</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
+      <c r="U33">
+        <v>8266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C34" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D34" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E34" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F34">
         <v>3172</v>
@@ -6187,22 +6292,25 @@
       <c r="T34">
         <v>4681</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
+      <c r="U34">
+        <v>4529</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C35" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D35" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E35" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F35">
         <v>5900</v>
@@ -6249,22 +6357,25 @@
       <c r="T35">
         <v>8542</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
+      <c r="U35">
+        <v>7703</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C36" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D36" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E36" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F36">
         <v>3917</v>
@@ -6311,22 +6422,25 @@
       <c r="T36">
         <v>5039</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
+      <c r="U36">
+        <v>4377</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C37" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D37" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E37" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F37">
         <v>2190</v>
@@ -6373,22 +6487,25 @@
       <c r="T37">
         <v>2601</v>
       </c>
-    </row>
-    <row r="38" spans="1:20">
+      <c r="U37">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C38" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D38" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E38" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F38">
         <v>34597</v>
@@ -6435,22 +6552,25 @@
       <c r="T38">
         <v>46067</v>
       </c>
-    </row>
-    <row r="39" spans="1:20">
+      <c r="U38">
+        <v>43654</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C39" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D39" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E39" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F39">
         <v>4397</v>
@@ -6497,22 +6617,25 @@
       <c r="T39">
         <v>7219</v>
       </c>
-    </row>
-    <row r="40" spans="1:20">
+      <c r="U39">
+        <v>5859</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C40" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D40" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E40" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F40">
         <v>1044</v>
@@ -6559,22 +6682,25 @@
       <c r="T40">
         <v>1154</v>
       </c>
-    </row>
-    <row r="41" spans="1:20">
+      <c r="U40">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C41" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D41" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E41" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F41">
         <v>1779</v>
@@ -6621,22 +6747,25 @@
       <c r="T41">
         <v>2348</v>
       </c>
-    </row>
-    <row r="42" spans="1:20">
+      <c r="U41">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C42" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D42" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E42" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F42">
         <v>2757</v>
@@ -6683,22 +6812,25 @@
       <c r="T42">
         <v>3858</v>
       </c>
-    </row>
-    <row r="43" spans="1:20">
+      <c r="U42">
+        <v>3912</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C43" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D43" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E43" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="F43">
         <v>2336</v>
@@ -6745,22 +6877,25 @@
       <c r="T43">
         <v>3629</v>
       </c>
-    </row>
-    <row r="44" spans="1:20">
+      <c r="U43">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C44" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D44" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E44" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="F44">
         <v>6000</v>
@@ -6807,22 +6942,25 @@
       <c r="T44">
         <v>7724</v>
       </c>
-    </row>
-    <row r="45" spans="1:20">
+      <c r="U44">
+        <v>7391</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C45" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D45" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E45" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="F45">
         <v>1514</v>
@@ -6869,22 +7007,25 @@
       <c r="T45">
         <v>2067</v>
       </c>
-    </row>
-    <row r="46" spans="1:20">
+      <c r="U45">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C46" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D46" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E46" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="F46">
         <v>2938</v>
@@ -6931,22 +7072,25 @@
       <c r="T46">
         <v>3816</v>
       </c>
-    </row>
-    <row r="47" spans="1:20">
+      <c r="U46">
+        <v>3666</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C47" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D47" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E47" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="F47">
         <v>267</v>
@@ -6993,22 +7137,25 @@
       <c r="T47">
         <v>354</v>
       </c>
-    </row>
-    <row r="48" spans="1:20">
+      <c r="U47">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C48" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D48" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E48" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="F48">
         <v>2426</v>
@@ -7055,22 +7202,25 @@
       <c r="T48">
         <v>3015</v>
       </c>
-    </row>
-    <row r="49" spans="1:20">
+      <c r="U48">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C49" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D49" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E49" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="F49">
         <v>2463</v>
@@ -7117,22 +7267,25 @@
       <c r="T49">
         <v>2905</v>
       </c>
-    </row>
-    <row r="50" spans="1:20">
+      <c r="U49">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C50" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D50" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E50" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="F50">
         <v>3343</v>
@@ -7179,22 +7332,25 @@
       <c r="T50">
         <v>4408</v>
       </c>
-    </row>
-    <row r="51" spans="1:20">
+      <c r="U50">
+        <v>4284</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C51" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D51" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E51" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="F51">
         <v>3333</v>
@@ -7241,22 +7397,25 @@
       <c r="T51">
         <v>3570</v>
       </c>
-    </row>
-    <row r="52" spans="1:20">
+      <c r="U51">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C52" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D52" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E52" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="F52">
         <v>25942</v>
@@ -7303,22 +7462,25 @@
       <c r="T52">
         <v>38561</v>
       </c>
-    </row>
-    <row r="53" spans="1:20">
+      <c r="U52">
+        <v>37393</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C53" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D53" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E53" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="F53">
         <v>2563</v>
@@ -7365,22 +7527,25 @@
       <c r="T53">
         <v>4408</v>
       </c>
-    </row>
-    <row r="54" spans="1:20">
+      <c r="U53">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C54" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D54" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E54" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F54">
         <v>940</v>
@@ -7427,22 +7592,25 @@
       <c r="T54">
         <v>1102</v>
       </c>
-    </row>
-    <row r="55" spans="1:20">
+      <c r="U54">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C55" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D55" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E55" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="F55">
         <v>3096</v>
@@ -7489,22 +7657,25 @@
       <c r="T55">
         <v>4920</v>
       </c>
-    </row>
-    <row r="56" spans="1:20">
+      <c r="U55">
+        <v>4861</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C56" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D56" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E56" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="F56">
         <v>3308</v>
@@ -7551,22 +7722,25 @@
       <c r="T56">
         <v>5156</v>
       </c>
-    </row>
-    <row r="57" spans="1:20">
+      <c r="U56">
+        <v>5059</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B57" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C57" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D57" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E57" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="F57">
         <v>4493</v>
@@ -7613,22 +7787,25 @@
       <c r="T57">
         <v>6982</v>
       </c>
-    </row>
-    <row r="58" spans="1:20">
+      <c r="U57">
+        <v>6742</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B58" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C58" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D58" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E58" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="F58">
         <v>1263</v>
@@ -7675,22 +7852,25 @@
       <c r="T58">
         <v>1523</v>
       </c>
-    </row>
-    <row r="59" spans="1:20">
+      <c r="U58">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B59" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C59" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D59" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E59" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="F59">
         <v>3386</v>
@@ -7737,22 +7917,25 @@
       <c r="T59">
         <v>5044</v>
       </c>
-    </row>
-    <row r="60" spans="1:20">
+      <c r="U59">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B60" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C60" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D60" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E60" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="F60">
         <v>1337</v>
@@ -7799,22 +7982,25 @@
       <c r="T60">
         <v>2481</v>
       </c>
-    </row>
-    <row r="61" spans="1:20">
+      <c r="U60">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B61" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C61" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D61" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E61" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="F61">
         <v>925</v>
@@ -7861,22 +8047,25 @@
       <c r="T61">
         <v>1060</v>
       </c>
-    </row>
-    <row r="62" spans="1:20">
+      <c r="U61">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B62" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C62" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D62" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E62" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="F62">
         <v>905</v>
@@ -7923,22 +8112,25 @@
       <c r="T62">
         <v>1230</v>
       </c>
-    </row>
-    <row r="63" spans="1:20">
+      <c r="U62">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B63" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C63" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D63" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E63" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="F63">
         <v>1368</v>
@@ -7985,22 +8177,25 @@
       <c r="T63">
         <v>1972</v>
       </c>
-    </row>
-    <row r="64" spans="1:20">
+      <c r="U63">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C64" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D64" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E64" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="F64">
         <v>1875</v>
@@ -8047,22 +8242,25 @@
       <c r="T64">
         <v>2081</v>
       </c>
-    </row>
-    <row r="65" spans="1:20">
+      <c r="U64">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B65" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C65" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D65" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E65" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="F65">
         <v>483</v>
@@ -8109,22 +8307,25 @@
       <c r="T65">
         <v>602</v>
       </c>
-    </row>
-    <row r="66" spans="1:20">
+      <c r="U65">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C66" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D66" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E66" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="F66">
         <v>63861</v>
@@ -8171,22 +8372,25 @@
       <c r="T66">
         <v>100909</v>
       </c>
-    </row>
-    <row r="67" spans="1:20">
+      <c r="U66">
+        <v>99656</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B67" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C67" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D67" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E67" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="F67">
         <v>4886</v>
@@ -8233,22 +8437,25 @@
       <c r="T67">
         <v>7338</v>
       </c>
-    </row>
-    <row r="68" spans="1:20">
+      <c r="U67">
+        <v>7194</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B68" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C68" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D68" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E68" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -8295,22 +8502,25 @@
       <c r="T68">
         <v>3541</v>
       </c>
-    </row>
-    <row r="69" spans="1:20">
+      <c r="U68">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B69" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C69" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D69" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E69" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -8357,22 +8567,25 @@
       <c r="T69">
         <v>6348</v>
       </c>
-    </row>
-    <row r="70" spans="1:20">
+      <c r="U69">
+        <v>6179</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B70" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C70" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D70" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E70" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="F70">
         <v>3835</v>
@@ -8419,22 +8632,25 @@
       <c r="T70">
         <v>6569</v>
       </c>
-    </row>
-    <row r="71" spans="1:20">
+      <c r="U70">
+        <v>6766</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C71" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D71" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E71" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="F71">
         <v>3070</v>
@@ -8481,22 +8697,25 @@
       <c r="T71">
         <v>4666</v>
       </c>
-    </row>
-    <row r="72" spans="1:20">
+      <c r="U71">
+        <v>4814</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B72" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C72" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D72" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E72" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="F72">
         <v>5558</v>
@@ -8543,22 +8762,25 @@
       <c r="T72">
         <v>8947</v>
       </c>
-    </row>
-    <row r="73" spans="1:20">
+      <c r="U72">
+        <v>9115</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B73" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C73" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D73" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E73" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="F73">
         <v>4574</v>
@@ -8605,22 +8827,25 @@
       <c r="T73">
         <v>7696</v>
       </c>
-    </row>
-    <row r="74" spans="1:20">
+      <c r="U73">
+        <v>7451</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B74" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C74" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D74" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E74" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="F74">
         <v>5527</v>
@@ -8667,22 +8892,25 @@
       <c r="T74">
         <v>9173</v>
       </c>
-    </row>
-    <row r="75" spans="1:20">
+      <c r="U74">
+        <v>9159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B75" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C75" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D75" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E75" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="F75">
         <v>5034</v>
@@ -8729,22 +8957,25 @@
       <c r="T75">
         <v>7640</v>
       </c>
-    </row>
-    <row r="76" spans="1:20">
+      <c r="U75">
+        <v>7513</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B76" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C76" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D76" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E76" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="F76">
         <v>2346</v>
@@ -8791,22 +9022,25 @@
       <c r="T76">
         <v>3472</v>
       </c>
-    </row>
-    <row r="77" spans="1:20">
+      <c r="U76">
+        <v>3418</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B77" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C77" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D77" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E77" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="F77">
         <v>1647</v>
@@ -8853,22 +9087,25 @@
       <c r="T77">
         <v>2532</v>
       </c>
-    </row>
-    <row r="78" spans="1:20">
+      <c r="U77">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B78" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C78" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D78" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E78" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="F78">
         <v>3010</v>
@@ -8915,22 +9152,25 @@
       <c r="T78">
         <v>4892</v>
       </c>
-    </row>
-    <row r="79" spans="1:20">
+      <c r="U78">
+        <v>4951</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C79" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D79" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E79" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="F79">
         <v>3769</v>
@@ -8977,22 +9217,25 @@
       <c r="T79">
         <v>6121</v>
       </c>
-    </row>
-    <row r="80" spans="1:20">
+      <c r="U79">
+        <v>5935</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B80" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C80" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D80" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E80" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="F80">
         <v>8141</v>
@@ -9039,22 +9282,25 @@
       <c r="T80">
         <v>8332</v>
       </c>
-    </row>
-    <row r="81" spans="1:20">
+      <c r="U80">
+        <v>8172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B81" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C81" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D81" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E81" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="F81">
         <v>7119</v>
@@ -9101,22 +9347,25 @@
       <c r="T81">
         <v>5776</v>
       </c>
-    </row>
-    <row r="82" spans="1:20">
+      <c r="U81">
+        <v>5307</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B82" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C82" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D82" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E82" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F82">
         <v>5345</v>
@@ -9163,22 +9412,25 @@
       <c r="T82">
         <v>7866</v>
       </c>
-    </row>
-    <row r="83" spans="1:20">
+      <c r="U82">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B83" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C83" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D83" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E83" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="F83">
         <v>18409</v>
@@ -9225,22 +9477,25 @@
       <c r="T83">
         <v>25763</v>
       </c>
-    </row>
-    <row r="84" spans="1:20">
+      <c r="U83">
+        <v>24127</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B84" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C84" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D84" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E84" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="F84">
         <v>2464</v>
@@ -9287,22 +9542,25 @@
       <c r="T84">
         <v>4433</v>
       </c>
-    </row>
-    <row r="85" spans="1:20">
+      <c r="U84">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B85" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C85" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D85" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E85" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="F85">
         <v>1579</v>
@@ -9349,22 +9607,25 @@
       <c r="T85">
         <v>2088</v>
       </c>
-    </row>
-    <row r="86" spans="1:20">
+      <c r="U85">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B86" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C86" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D86" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E86" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -9411,22 +9672,25 @@
       <c r="T86">
         <v>167</v>
       </c>
-    </row>
-    <row r="87" spans="1:20">
+      <c r="U86">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B87" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C87" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D87" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E87" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F87">
         <v>837</v>
@@ -9473,22 +9737,25 @@
       <c r="T87">
         <v>699</v>
       </c>
-    </row>
-    <row r="88" spans="1:20">
+      <c r="U87">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B88" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C88" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D88" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E88" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="F88">
         <v>2746</v>
@@ -9535,22 +9802,25 @@
       <c r="T88">
         <v>3890</v>
       </c>
-    </row>
-    <row r="89" spans="1:20">
+      <c r="U88">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C89" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D89" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E89" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="F89">
         <v>2024</v>
@@ -9597,22 +9867,25 @@
       <c r="T89">
         <v>2763</v>
       </c>
-    </row>
-    <row r="90" spans="1:20">
+      <c r="U89">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B90" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C90" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D90" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E90" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="F90">
         <v>2278</v>
@@ -9659,22 +9932,25 @@
       <c r="T90">
         <v>3307</v>
       </c>
-    </row>
-    <row r="91" spans="1:20">
+      <c r="U90">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B91" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C91" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D91" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E91" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="F91">
         <v>1728</v>
@@ -9721,22 +9997,25 @@
       <c r="T91">
         <v>2270</v>
       </c>
-    </row>
-    <row r="92" spans="1:20">
+      <c r="U91">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B92" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C92" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D92" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E92" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="F92">
         <v>282</v>
@@ -9783,22 +10062,25 @@
       <c r="T92">
         <v>202</v>
       </c>
-    </row>
-    <row r="93" spans="1:20">
+      <c r="U92">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B93" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C93" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D93" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E93" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="F93">
         <v>870</v>
@@ -9845,22 +10127,25 @@
       <c r="T93">
         <v>728</v>
       </c>
-    </row>
-    <row r="94" spans="1:20">
+      <c r="U93">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B94" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C94" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D94" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E94" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="F94">
         <v>3601</v>
@@ -9907,22 +10192,25 @@
       <c r="T94">
         <v>5216</v>
       </c>
-    </row>
-    <row r="95" spans="1:20">
+      <c r="U94">
+        <v>4929</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B95" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C95" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D95" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E95" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="F95">
         <v>50799</v>
@@ -9969,22 +10257,25 @@
       <c r="T95">
         <v>81930</v>
       </c>
-    </row>
-    <row r="96" spans="1:20">
+      <c r="U95">
+        <v>75689</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B96" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C96" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D96" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E96" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F96">
         <v>10419</v>
@@ -10031,22 +10322,25 @@
       <c r="T96">
         <v>20317</v>
       </c>
-    </row>
-    <row r="97" spans="1:20">
+      <c r="U96">
+        <v>18524</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B97" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C97" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D97" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E97" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="F97">
         <v>2063</v>
@@ -10093,22 +10387,25 @@
       <c r="T97">
         <v>3427</v>
       </c>
-    </row>
-    <row r="98" spans="1:20">
+      <c r="U97">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B98" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C98" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D98" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E98" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="F98">
         <v>4211</v>
@@ -10155,22 +10452,25 @@
       <c r="T98">
         <v>6167</v>
       </c>
-    </row>
-    <row r="99" spans="1:20">
+      <c r="U98">
+        <v>5660</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B99" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C99" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D99" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E99" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="F99">
         <v>4475</v>
@@ -10217,22 +10517,25 @@
       <c r="T99">
         <v>5306</v>
       </c>
-    </row>
-    <row r="100" spans="1:20">
+      <c r="U99">
+        <v>4887</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21">
       <c r="A100" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B100" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C100" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D100" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E100" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="F100">
         <v>2915</v>
@@ -10279,22 +10582,25 @@
       <c r="T100">
         <v>4353</v>
       </c>
-    </row>
-    <row r="101" spans="1:20">
+      <c r="U100">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21">
       <c r="A101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B101" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C101" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D101" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E101" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F101">
         <v>3976</v>
@@ -10341,22 +10647,25 @@
       <c r="T101">
         <v>5604</v>
       </c>
-    </row>
-    <row r="102" spans="1:20">
+      <c r="U101">
+        <v>5169</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21">
       <c r="A102" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B102" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C102" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D102" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E102" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="F102">
         <v>3812</v>
@@ -10403,22 +10712,25 @@
       <c r="T102">
         <v>6684</v>
       </c>
-    </row>
-    <row r="103" spans="1:20">
+      <c r="U102">
+        <v>6231</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21">
       <c r="A103" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B103" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C103" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D103" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E103" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="F103">
         <v>4258</v>
@@ -10465,22 +10777,25 @@
       <c r="T103">
         <v>6451</v>
       </c>
-    </row>
-    <row r="104" spans="1:20">
+      <c r="U103">
+        <v>5917</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B104" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C104" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D104" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E104" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="F104">
         <v>3113</v>
@@ -10527,22 +10842,25 @@
       <c r="T104">
         <v>4720</v>
       </c>
-    </row>
-    <row r="105" spans="1:20">
+      <c r="U104">
+        <v>4366</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21">
       <c r="A105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B105" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C105" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D105" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E105" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="F105">
         <v>3339</v>
@@ -10589,22 +10907,25 @@
       <c r="T105">
         <v>5577</v>
       </c>
-    </row>
-    <row r="106" spans="1:20">
+      <c r="U105">
+        <v>5272</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21">
       <c r="A106" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B106" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C106" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D106" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E106" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="F106">
         <v>4449</v>
@@ -10651,22 +10972,25 @@
       <c r="T106">
         <v>7399</v>
       </c>
-    </row>
-    <row r="107" spans="1:20">
+      <c r="U106">
+        <v>6838</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21">
       <c r="A107" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B107" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C107" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D107" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E107" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="F107">
         <v>3769</v>
@@ -10713,22 +11037,25 @@
       <c r="T107">
         <v>5925</v>
       </c>
-    </row>
-    <row r="108" spans="1:20">
+      <c r="U107">
+        <v>5640</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21">
       <c r="A108" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B108" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C108" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D108" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E108" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="F108">
         <v>75213</v>
@@ -10775,22 +11102,25 @@
       <c r="T108">
         <v>110865</v>
       </c>
-    </row>
-    <row r="109" spans="1:20">
+      <c r="U108">
+        <v>106266</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21">
       <c r="A109" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B109" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C109" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D109" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E109" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="F109">
         <v>6659</v>
@@ -10837,22 +11167,25 @@
       <c r="T109">
         <v>12742</v>
       </c>
-    </row>
-    <row r="110" spans="1:20">
+      <c r="U109">
+        <v>11819</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21">
       <c r="A110" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B110" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C110" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D110" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E110" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="F110">
         <v>1802</v>
@@ -10899,22 +11232,25 @@
       <c r="T110">
         <v>1861</v>
       </c>
-    </row>
-    <row r="111" spans="1:20">
+      <c r="U110">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21">
       <c r="A111" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B111" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C111" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D111" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E111" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F111">
         <v>2975</v>
@@ -10961,22 +11297,25 @@
       <c r="T111">
         <v>4630</v>
       </c>
-    </row>
-    <row r="112" spans="1:20">
+      <c r="U111">
+        <v>4462</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21">
       <c r="A112" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B112" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C112" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D112" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E112" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="F112">
         <v>3845</v>
@@ -11023,22 +11362,25 @@
       <c r="T112">
         <v>5863</v>
       </c>
-    </row>
-    <row r="113" spans="1:20">
+      <c r="U112">
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21">
       <c r="A113" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C113" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D113" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E113" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="F113">
         <v>3049</v>
@@ -11085,22 +11427,25 @@
       <c r="T113">
         <v>5368</v>
       </c>
-    </row>
-    <row r="114" spans="1:20">
+      <c r="U113">
+        <v>5085</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21">
       <c r="A114" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B114" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C114" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D114" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E114" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="F114">
         <v>4924</v>
@@ -11147,22 +11492,25 @@
       <c r="T114">
         <v>7848</v>
       </c>
-    </row>
-    <row r="115" spans="1:20">
+      <c r="U114">
+        <v>7440</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21">
       <c r="A115" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B115" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C115" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D115" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E115" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="F115">
         <v>5286</v>
@@ -11209,22 +11557,25 @@
       <c r="T115">
         <v>7771</v>
       </c>
-    </row>
-    <row r="116" spans="1:20">
+      <c r="U115">
+        <v>7719</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21">
       <c r="A116" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B116" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C116" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D116" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E116" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="F116">
         <v>2875</v>
@@ -11271,22 +11622,25 @@
       <c r="T116">
         <v>3635</v>
       </c>
-    </row>
-    <row r="117" spans="1:20">
+      <c r="U116">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21">
       <c r="A117" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B117" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C117" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D117" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E117" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="F117">
         <v>3928</v>
@@ -11333,22 +11687,25 @@
       <c r="T117">
         <v>5568</v>
       </c>
-    </row>
-    <row r="118" spans="1:20">
+      <c r="U117">
+        <v>5415</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21">
       <c r="A118" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B118" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C118" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D118" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E118" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="F118">
         <v>5212</v>
@@ -11395,22 +11752,25 @@
       <c r="T118">
         <v>7995</v>
       </c>
-    </row>
-    <row r="119" spans="1:20">
+      <c r="U118">
+        <v>7464</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21">
       <c r="A119" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B119" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C119" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D119" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E119" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F119">
         <v>7199</v>
@@ -11457,22 +11817,25 @@
       <c r="T119">
         <v>10379</v>
       </c>
-    </row>
-    <row r="120" spans="1:20">
+      <c r="U119">
+        <v>9782</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21">
       <c r="A120" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B120" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C120" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D120" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E120" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="F120">
         <v>2741</v>
@@ -11519,22 +11882,25 @@
       <c r="T120">
         <v>3759</v>
       </c>
-    </row>
-    <row r="121" spans="1:20">
+      <c r="U120">
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B121" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C121" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D121" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E121" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="F121">
         <v>6851</v>
@@ -11581,22 +11947,25 @@
       <c r="T121">
         <v>6666</v>
       </c>
-    </row>
-    <row r="122" spans="1:20">
+      <c r="U121">
+        <v>6332</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21">
       <c r="A122" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B122" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C122" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D122" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E122" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="F122">
         <v>3297</v>
@@ -11643,22 +12012,25 @@
       <c r="T122">
         <v>4230</v>
       </c>
-    </row>
-    <row r="123" spans="1:20">
+      <c r="U122">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21">
       <c r="A123" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B123" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C123" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D123" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E123" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F123">
         <v>10903</v>
@@ -11705,22 +12077,25 @@
       <c r="T123">
         <v>16402</v>
       </c>
-    </row>
-    <row r="124" spans="1:20">
+      <c r="U123">
+        <v>16212</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21">
       <c r="A124" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B124" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C124" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D124" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E124" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="F124">
         <v>3667</v>
@@ -11767,22 +12142,25 @@
       <c r="T124">
         <v>6148</v>
       </c>
-    </row>
-    <row r="125" spans="1:20">
+      <c r="U124">
+        <v>5935</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21">
       <c r="A125" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B125" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C125" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D125" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E125" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="F125">
         <v>51103</v>
@@ -11829,22 +12207,25 @@
       <c r="T125">
         <v>84054</v>
       </c>
-    </row>
-    <row r="126" spans="1:20">
+      <c r="U125">
+        <v>81885</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21">
       <c r="A126" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B126" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C126" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D126" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E126" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="F126">
         <v>2755</v>
@@ -11891,22 +12272,25 @@
       <c r="T126">
         <v>5168</v>
       </c>
-    </row>
-    <row r="127" spans="1:20">
+      <c r="U126">
+        <v>4830</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21">
       <c r="A127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B127" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C127" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D127" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E127" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="F127">
         <v>2775</v>
@@ -11953,22 +12337,25 @@
       <c r="T127">
         <v>5871</v>
       </c>
-    </row>
-    <row r="128" spans="1:20">
+      <c r="U127">
+        <v>5636</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21">
       <c r="A128" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B128" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C128" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D128" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E128" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="F128">
         <v>2462</v>
@@ -12015,22 +12402,25 @@
       <c r="T128">
         <v>3903</v>
       </c>
-    </row>
-    <row r="129" spans="1:20">
+      <c r="U128">
+        <v>3803</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21">
       <c r="A129" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B129" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C129" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D129" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E129" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -12077,22 +12467,25 @@
       <c r="T129">
         <v>2668</v>
       </c>
-    </row>
-    <row r="130" spans="1:20">
+      <c r="U129">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21">
       <c r="A130" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B130" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C130" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D130" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E130" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="F130">
         <v>2420</v>
@@ -12139,22 +12532,25 @@
       <c r="T130">
         <v>3512</v>
       </c>
-    </row>
-    <row r="131" spans="1:20">
+      <c r="U130">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21">
       <c r="A131" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B131" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C131" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D131" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E131" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="F131">
         <v>2965</v>
@@ -12201,22 +12597,25 @@
       <c r="T131">
         <v>4282</v>
       </c>
-    </row>
-    <row r="132" spans="1:20">
+      <c r="U131">
+        <v>4174</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21">
       <c r="A132" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B132" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C132" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D132" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E132" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="F132">
         <v>8095</v>
@@ -12263,22 +12662,25 @@
       <c r="T132">
         <v>12754</v>
       </c>
-    </row>
-    <row r="133" spans="1:20">
+      <c r="U132">
+        <v>12406</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21">
       <c r="A133" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B133" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C133" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D133" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E133" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F133">
         <v>3819</v>
@@ -12325,22 +12727,25 @@
       <c r="T133">
         <v>7079</v>
       </c>
-    </row>
-    <row r="134" spans="1:20">
+      <c r="U133">
+        <v>6987</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21">
       <c r="A134" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B134" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C134" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D134" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E134" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="F134">
         <v>3397</v>
@@ -12387,22 +12792,25 @@
       <c r="T134">
         <v>7613</v>
       </c>
-    </row>
-    <row r="135" spans="1:20">
+      <c r="U134">
+        <v>7215</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21">
       <c r="A135" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B135" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C135" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D135" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E135" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="F135">
         <v>3904</v>
@@ -12449,22 +12857,25 @@
       <c r="T135">
         <v>3768</v>
       </c>
-    </row>
-    <row r="136" spans="1:20">
+      <c r="U135">
+        <v>3533</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21">
       <c r="A136" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B136" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C136" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D136" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E136" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="F136">
         <v>5453</v>
@@ -12511,22 +12922,25 @@
       <c r="T136">
         <v>6417</v>
       </c>
-    </row>
-    <row r="137" spans="1:20">
+      <c r="U136">
+        <v>6465</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21">
       <c r="A137" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B137" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C137" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D137" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E137" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="F137">
         <v>2210</v>
@@ -12573,22 +12987,25 @@
       <c r="T137">
         <v>2766</v>
       </c>
-    </row>
-    <row r="138" spans="1:20">
+      <c r="U137">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21">
       <c r="A138" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B138" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C138" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D138" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E138" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="F138">
         <v>3483</v>
@@ -12635,22 +13052,25 @@
       <c r="T138">
         <v>5657</v>
       </c>
-    </row>
-    <row r="139" spans="1:20">
+      <c r="U138">
+        <v>5445</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21">
       <c r="A139" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B139" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C139" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D139" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E139" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F139">
         <v>3165</v>
@@ -12697,22 +13117,25 @@
       <c r="T139">
         <v>5615</v>
       </c>
-    </row>
-    <row r="140" spans="1:20">
+      <c r="U139">
+        <v>5572</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21">
       <c r="A140" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B140" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C140" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D140" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E140" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F140">
         <v>4200</v>
@@ -12759,22 +13182,25 @@
       <c r="T140">
         <v>6981</v>
       </c>
-    </row>
-    <row r="141" spans="1:20">
+      <c r="U140">
+        <v>6890</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21">
       <c r="A141" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B141" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C141" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D141" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E141" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="F141">
         <v>16260</v>
@@ -12821,22 +13247,25 @@
       <c r="T141">
         <v>22113</v>
       </c>
-    </row>
-    <row r="142" spans="1:20">
+      <c r="U141">
+        <v>21042</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21">
       <c r="A142" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B142" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C142" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D142" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E142" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="F142">
         <v>1549</v>
@@ -12883,22 +13312,25 @@
       <c r="T142">
         <v>2911</v>
       </c>
-    </row>
-    <row r="143" spans="1:20">
+      <c r="U142">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21">
       <c r="A143" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B143" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C143" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D143" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E143" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="F143">
         <v>395</v>
@@ -12945,22 +13377,25 @@
       <c r="T143">
         <v>204</v>
       </c>
-    </row>
-    <row r="144" spans="1:20">
+      <c r="U143">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21">
       <c r="A144" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B144" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C144" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D144" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E144" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="F144">
         <v>729</v>
@@ -13007,22 +13442,25 @@
       <c r="T144">
         <v>1127</v>
       </c>
-    </row>
-    <row r="145" spans="1:20">
+      <c r="U144">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B145" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C145" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D145" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E145" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="F145">
         <v>1013</v>
@@ -13069,22 +13507,25 @@
       <c r="T145">
         <v>1228</v>
       </c>
-    </row>
-    <row r="146" spans="1:20">
+      <c r="U145">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21">
       <c r="A146" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B146" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C146" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D146" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E146" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="F146">
         <v>2458</v>
@@ -13131,22 +13572,25 @@
       <c r="T146">
         <v>3430</v>
       </c>
-    </row>
-    <row r="147" spans="1:20">
+      <c r="U146">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21">
       <c r="A147" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B147" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C147" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D147" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E147" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="F147">
         <v>1547</v>
@@ -13193,22 +13637,25 @@
       <c r="T147">
         <v>1914</v>
       </c>
-    </row>
-    <row r="148" spans="1:20">
+      <c r="U147">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21">
       <c r="A148" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B148" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C148" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D148" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E148" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="F148">
         <v>1497</v>
@@ -13255,22 +13702,25 @@
       <c r="T148">
         <v>1929</v>
       </c>
-    </row>
-    <row r="149" spans="1:20">
+      <c r="U148">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21">
       <c r="A149" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B149" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C149" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D149" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E149" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F149">
         <v>1314</v>
@@ -13317,22 +13767,25 @@
       <c r="T149">
         <v>1613</v>
       </c>
-    </row>
-    <row r="150" spans="1:20">
+      <c r="U149">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21">
       <c r="A150" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B150" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C150" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D150" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E150" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="F150">
         <v>1440</v>
@@ -13379,22 +13832,25 @@
       <c r="T150">
         <v>2012</v>
       </c>
-    </row>
-    <row r="151" spans="1:20">
+      <c r="U150">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21">
       <c r="A151" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B151" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C151" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D151" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E151" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="F151">
         <v>2380</v>
@@ -13441,22 +13897,25 @@
       <c r="T151">
         <v>3162</v>
       </c>
-    </row>
-    <row r="152" spans="1:20">
+      <c r="U151">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21">
       <c r="A152" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B152" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C152" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D152" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E152" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F152">
         <v>1938</v>
@@ -13503,22 +13962,25 @@
       <c r="T152">
         <v>2583</v>
       </c>
-    </row>
-    <row r="153" spans="1:20">
+      <c r="U152">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21">
       <c r="A153" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B153" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C153" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D153" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E153" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="F153">
         <v>54830</v>
@@ -13565,22 +14027,25 @@
       <c r="T153">
         <v>69576</v>
       </c>
-    </row>
-    <row r="154" spans="1:20">
+      <c r="U153">
+        <v>64245</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21">
       <c r="A154" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B154" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C154" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D154" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E154" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -13627,22 +14092,25 @@
       <c r="T154">
         <v>1067</v>
       </c>
-    </row>
-    <row r="155" spans="1:20">
+      <c r="U154">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21">
       <c r="A155" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B155" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C155" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D155" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E155" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="F155">
         <v>2456</v>
@@ -13689,22 +14157,25 @@
       <c r="T155">
         <v>3176</v>
       </c>
-    </row>
-    <row r="156" spans="1:20">
+      <c r="U155">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21">
       <c r="A156" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B156" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C156" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D156" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E156" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="F156">
         <v>3466</v>
@@ -13751,22 +14222,25 @@
       <c r="T156">
         <v>3779</v>
       </c>
-    </row>
-    <row r="157" spans="1:20">
+      <c r="U156">
+        <v>3685</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21">
       <c r="A157" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B157" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C157" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D157" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E157" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="F157">
         <v>1903</v>
@@ -13813,22 +14287,25 @@
       <c r="T157">
         <v>2223</v>
       </c>
-    </row>
-    <row r="158" spans="1:20">
+      <c r="U157">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21">
       <c r="A158" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B158" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C158" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D158" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E158" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="F158">
         <v>2436</v>
@@ -13875,22 +14352,25 @@
       <c r="T158">
         <v>2799</v>
       </c>
-    </row>
-    <row r="159" spans="1:20">
+      <c r="U158">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21">
       <c r="A159" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B159" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C159" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D159" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E159" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -13937,22 +14417,25 @@
       <c r="T159">
         <v>468</v>
       </c>
-    </row>
-    <row r="160" spans="1:20">
+      <c r="U159">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21">
       <c r="A160" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B160" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C160" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D160" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E160" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -13999,22 +14482,25 @@
       <c r="T160">
         <v>1727</v>
       </c>
-    </row>
-    <row r="161" spans="1:20">
+      <c r="U160">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21">
       <c r="A161" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B161" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C161" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D161" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E161" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="F161">
         <v>2011</v>
@@ -14061,22 +14547,25 @@
       <c r="T161">
         <v>2590</v>
       </c>
-    </row>
-    <row r="162" spans="1:20">
+      <c r="U161">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21">
       <c r="A162" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B162" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C162" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D162" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E162" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F162">
         <v>2500</v>
@@ -14123,22 +14612,25 @@
       <c r="T162">
         <v>2891</v>
       </c>
-    </row>
-    <row r="163" spans="1:20">
+      <c r="U162">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21">
       <c r="A163" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B163" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C163" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D163" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E163" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="F163">
         <v>3290</v>
@@ -14185,22 +14677,25 @@
       <c r="T163">
         <v>4065</v>
       </c>
-    </row>
-    <row r="164" spans="1:20">
+      <c r="U163">
+        <v>3695</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21">
       <c r="A164" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B164" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C164" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D164" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E164" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="F164">
         <v>3182</v>
@@ -14247,22 +14742,25 @@
       <c r="T164">
         <v>3493</v>
       </c>
-    </row>
-    <row r="165" spans="1:20">
+      <c r="U164">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21">
       <c r="A165" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B165" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C165" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D165" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E165" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="F165">
         <v>2516</v>
@@ -14309,22 +14807,25 @@
       <c r="T165">
         <v>3239</v>
       </c>
-    </row>
-    <row r="166" spans="1:20">
+      <c r="U165">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21">
       <c r="A166" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B166" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C166" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D166" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E166" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="F166">
         <v>2180</v>
@@ -14371,22 +14872,25 @@
       <c r="T166">
         <v>2737</v>
       </c>
-    </row>
-    <row r="167" spans="1:20">
+      <c r="U166">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21">
       <c r="A167" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B167" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C167" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D167" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E167" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="F167">
         <v>7100</v>
@@ -14433,22 +14937,25 @@
       <c r="T167">
         <v>3971</v>
       </c>
-    </row>
-    <row r="168" spans="1:20">
+      <c r="U167">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21">
       <c r="A168" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B168" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C168" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D168" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E168" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="F168">
         <v>2540</v>
@@ -14495,22 +15002,25 @@
       <c r="T168">
         <v>3090</v>
       </c>
-    </row>
-    <row r="169" spans="1:20">
+      <c r="U168">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21">
       <c r="A169" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B169" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C169" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D169" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E169" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="F169">
         <v>3730</v>
@@ -14557,22 +15067,25 @@
       <c r="T169">
         <v>3975</v>
       </c>
-    </row>
-    <row r="170" spans="1:20">
+      <c r="U169">
+        <v>3682</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21">
       <c r="A170" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B170" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C170" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D170" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E170" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="F170">
         <v>2881</v>
@@ -14619,22 +15132,25 @@
       <c r="T170">
         <v>4719</v>
       </c>
-    </row>
-    <row r="171" spans="1:20">
+      <c r="U170">
+        <v>4044</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21">
       <c r="A171" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B171" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C171" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D171" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E171" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="F171">
         <v>1707</v>
@@ -14681,22 +15197,25 @@
       <c r="T171">
         <v>2464</v>
       </c>
-    </row>
-    <row r="172" spans="1:20">
+      <c r="U171">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21">
       <c r="A172" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B172" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C172" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D172" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E172" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="F172">
         <v>3372</v>
@@ -14743,22 +15262,25 @@
       <c r="T172">
         <v>3622</v>
       </c>
-    </row>
-    <row r="173" spans="1:20">
+      <c r="U172">
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21">
       <c r="A173" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B173" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C173" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D173" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E173" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="F173">
         <v>2520</v>
@@ -14805,22 +15327,25 @@
       <c r="T173">
         <v>3440</v>
       </c>
-    </row>
-    <row r="174" spans="1:20">
+      <c r="U173">
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21">
       <c r="A174" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B174" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C174" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D174" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E174" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="F174">
         <v>5040</v>
@@ -14867,22 +15392,25 @@
       <c r="T174">
         <v>4909</v>
       </c>
-    </row>
-    <row r="175" spans="1:20">
+      <c r="U174">
+        <v>4706</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21">
       <c r="A175" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B175" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C175" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D175" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E175" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -14929,22 +15457,25 @@
       <c r="T175">
         <v>5132</v>
       </c>
-    </row>
-    <row r="176" spans="1:20">
+      <c r="U175">
+        <v>4814</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21">
       <c r="A176" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B176" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C176" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D176" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E176" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="F176">
         <v>70622</v>
@@ -14991,22 +15522,25 @@
       <c r="T176">
         <v>103062</v>
       </c>
-    </row>
-    <row r="177" spans="1:20">
+      <c r="U176">
+        <v>98319</v>
+      </c>
+    </row>
+    <row r="177" spans="1:21">
       <c r="A177" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B177" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C177" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D177" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E177" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="F177">
         <v>4477</v>
@@ -15053,22 +15587,25 @@
       <c r="T177">
         <v>6871</v>
       </c>
-    </row>
-    <row r="178" spans="1:20">
+      <c r="U177">
+        <v>6226</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21">
       <c r="A178" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B178" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C178" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D178" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E178" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="F178">
         <v>4824</v>
@@ -15115,22 +15652,25 @@
       <c r="T178">
         <v>7654</v>
       </c>
-    </row>
-    <row r="179" spans="1:20">
+      <c r="U178">
+        <v>6923</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21">
       <c r="A179" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B179" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C179" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D179" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E179" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="F179">
         <v>1626</v>
@@ -15177,22 +15717,25 @@
       <c r="T179">
         <v>2339</v>
       </c>
-    </row>
-    <row r="180" spans="1:20">
+      <c r="U179">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21">
       <c r="A180" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B180" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C180" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D180" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E180" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="F180">
         <v>4459</v>
@@ -15239,22 +15782,25 @@
       <c r="T180">
         <v>6417</v>
       </c>
-    </row>
-    <row r="181" spans="1:20">
+      <c r="U180">
+        <v>5917</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21">
       <c r="A181" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B181" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C181" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D181" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E181" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="F181">
         <v>3875</v>
@@ -15301,22 +15847,25 @@
       <c r="T181">
         <v>5947</v>
       </c>
-    </row>
-    <row r="182" spans="1:20">
+      <c r="U181">
+        <v>5657</v>
+      </c>
+    </row>
+    <row r="182" spans="1:21">
       <c r="A182" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B182" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C182" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D182" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E182" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F182">
         <v>3424</v>
@@ -15363,22 +15912,25 @@
       <c r="T182">
         <v>5907</v>
       </c>
-    </row>
-    <row r="183" spans="1:20">
+      <c r="U182">
+        <v>5426</v>
+      </c>
+    </row>
+    <row r="183" spans="1:21">
       <c r="A183" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B183" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C183" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D183" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E183" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="F183">
         <v>4310</v>
@@ -15425,22 +15977,25 @@
       <c r="T183">
         <v>6407</v>
       </c>
-    </row>
-    <row r="184" spans="1:20">
+      <c r="U183">
+        <v>6077</v>
+      </c>
+    </row>
+    <row r="184" spans="1:21">
       <c r="A184" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B184" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C184" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D184" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E184" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="F184">
         <v>4614</v>
@@ -15487,22 +16042,25 @@
       <c r="T184">
         <v>6655</v>
       </c>
-    </row>
-    <row r="185" spans="1:20">
+      <c r="U184">
+        <v>6634</v>
+      </c>
+    </row>
+    <row r="185" spans="1:21">
       <c r="A185" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B185" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C185" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D185" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E185" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="F185">
         <v>4483</v>
@@ -15549,22 +16107,25 @@
       <c r="T185">
         <v>5922</v>
       </c>
-    </row>
-    <row r="186" spans="1:20">
+      <c r="U185">
+        <v>5610</v>
+      </c>
+    </row>
+    <row r="186" spans="1:21">
       <c r="A186" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B186" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C186" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D186" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E186" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F186">
         <v>4666</v>
@@ -15611,22 +16172,25 @@
       <c r="T186">
         <v>6430</v>
       </c>
-    </row>
-    <row r="187" spans="1:20">
+      <c r="U186">
+        <v>6237</v>
+      </c>
+    </row>
+    <row r="187" spans="1:21">
       <c r="A187" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B187" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C187" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D187" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E187" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="F187">
         <v>4423</v>
@@ -15673,22 +16237,25 @@
       <c r="T187">
         <v>7028</v>
       </c>
-    </row>
-    <row r="188" spans="1:20">
+      <c r="U187">
+        <v>6654</v>
+      </c>
+    </row>
+    <row r="188" spans="1:21">
       <c r="A188" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B188" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C188" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D188" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E188" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F188">
         <v>3900</v>
@@ -15735,22 +16302,25 @@
       <c r="T188">
         <v>5481</v>
       </c>
-    </row>
-    <row r="189" spans="1:20">
+      <c r="U188">
+        <v>5267</v>
+      </c>
+    </row>
+    <row r="189" spans="1:21">
       <c r="A189" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B189" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C189" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D189" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E189" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="F189">
         <v>1898</v>
@@ -15797,22 +16367,25 @@
       <c r="T189">
         <v>2050</v>
       </c>
-    </row>
-    <row r="190" spans="1:20">
+      <c r="U189">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="190" spans="1:21">
       <c r="A190" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B190" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C190" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D190" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E190" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F190">
         <v>3318</v>
@@ -15859,22 +16432,25 @@
       <c r="T190">
         <v>5514</v>
       </c>
-    </row>
-    <row r="191" spans="1:20">
+      <c r="U190">
+        <v>5494</v>
+      </c>
+    </row>
+    <row r="191" spans="1:21">
       <c r="A191" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B191" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C191" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D191" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E191" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="F191">
         <v>4568</v>
@@ -15921,22 +16497,25 @@
       <c r="T191">
         <v>5703</v>
       </c>
-    </row>
-    <row r="192" spans="1:20">
+      <c r="U191">
+        <v>5686</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21">
       <c r="A192" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B192" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C192" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D192" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E192" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F192">
         <v>4051</v>
@@ -15983,22 +16562,25 @@
       <c r="T192">
         <v>5653</v>
       </c>
-    </row>
-    <row r="193" spans="1:20">
+      <c r="U192">
+        <v>5401</v>
+      </c>
+    </row>
+    <row r="193" spans="1:21">
       <c r="A193" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B193" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C193" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D193" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E193" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="F193">
         <v>3296</v>
@@ -16045,22 +16627,25 @@
       <c r="T193">
         <v>4961</v>
       </c>
-    </row>
-    <row r="194" spans="1:20">
+      <c r="U193">
+        <v>4779</v>
+      </c>
+    </row>
+    <row r="194" spans="1:21">
       <c r="A194" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B194" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C194" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D194" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E194" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F194">
         <v>2211</v>
@@ -16107,22 +16692,25 @@
       <c r="T194">
         <v>3231</v>
       </c>
-    </row>
-    <row r="195" spans="1:20">
+      <c r="U194">
+        <v>3113</v>
+      </c>
+    </row>
+    <row r="195" spans="1:21">
       <c r="A195" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B195" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C195" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D195" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E195" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="F195">
         <v>2199</v>
@@ -16169,22 +16757,25 @@
       <c r="T195">
         <v>2892</v>
       </c>
-    </row>
-    <row r="196" spans="1:20">
+      <c r="U195">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="196" spans="1:21">
       <c r="A196" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B196" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C196" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D196" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E196" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="F196">
         <v>35965</v>
@@ -16231,22 +16822,25 @@
       <c r="T196">
         <v>47423</v>
       </c>
-    </row>
-    <row r="197" spans="1:20">
+      <c r="U196">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="197" spans="1:21">
       <c r="A197" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B197" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C197" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D197" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E197" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="F197">
         <v>2836</v>
@@ -16293,22 +16887,25 @@
       <c r="T197">
         <v>3825</v>
       </c>
-    </row>
-    <row r="198" spans="1:20">
+      <c r="U197">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="198" spans="1:21">
       <c r="A198" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B198" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C198" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D198" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E198" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -16355,22 +16952,25 @@
       <c r="T198">
         <v>2173</v>
       </c>
-    </row>
-    <row r="199" spans="1:20">
+      <c r="U198">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="199" spans="1:21">
       <c r="A199" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B199" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C199" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D199" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E199" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="F199">
         <v>3017</v>
@@ -16417,22 +17017,25 @@
       <c r="T199">
         <v>4431</v>
       </c>
-    </row>
-    <row r="200" spans="1:20">
+      <c r="U199">
+        <v>4359</v>
+      </c>
+    </row>
+    <row r="200" spans="1:21">
       <c r="A200" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B200" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C200" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D200" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E200" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F200">
         <v>2887</v>
@@ -16479,22 +17082,25 @@
       <c r="T200">
         <v>3620</v>
       </c>
-    </row>
-    <row r="201" spans="1:20">
+      <c r="U200">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="201" spans="1:21">
       <c r="A201" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B201" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C201" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D201" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E201" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="F201">
         <v>3272</v>
@@ -16541,22 +17147,25 @@
       <c r="T201">
         <v>4190</v>
       </c>
-    </row>
-    <row r="202" spans="1:20">
+      <c r="U201">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="202" spans="1:21">
       <c r="A202" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B202" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C202" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D202" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E202" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F202">
         <v>3780</v>
@@ -16603,22 +17212,25 @@
       <c r="T202">
         <v>4624</v>
       </c>
-    </row>
-    <row r="203" spans="1:20">
+      <c r="U202">
+        <v>4580</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21">
       <c r="A203" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B203" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C203" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D203" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E203" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="F203">
         <v>5086</v>
@@ -16665,22 +17277,25 @@
       <c r="T203">
         <v>5438</v>
       </c>
-    </row>
-    <row r="204" spans="1:20">
+      <c r="U203">
+        <v>5294</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21">
       <c r="A204" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B204" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C204" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D204" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E204" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -16727,22 +17342,25 @@
       <c r="T204">
         <v>1419</v>
       </c>
-    </row>
-    <row r="205" spans="1:20">
+      <c r="U204">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21">
       <c r="A205" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B205" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C205" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D205" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E205" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="F205">
         <v>3553</v>
@@ -16789,22 +17407,25 @@
       <c r="T205">
         <v>4817</v>
       </c>
-    </row>
-    <row r="206" spans="1:20">
+      <c r="U205">
+        <v>4621</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21">
       <c r="A206" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B206" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C206" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D206" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E206" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="F206">
         <v>4697</v>
@@ -16851,22 +17472,25 @@
       <c r="T206">
         <v>3866</v>
       </c>
-    </row>
-    <row r="207" spans="1:20">
+      <c r="U206">
+        <v>3866</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21">
       <c r="A207" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B207" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C207" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D207" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E207" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="F207">
         <v>3101</v>
@@ -16913,22 +17537,25 @@
       <c r="T207">
         <v>4303</v>
       </c>
-    </row>
-    <row r="208" spans="1:20">
+      <c r="U207">
+        <v>4167</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21">
       <c r="A208" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B208" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C208" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D208" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E208" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="F208">
         <v>2061</v>
@@ -16975,22 +17602,25 @@
       <c r="T208">
         <v>2677</v>
       </c>
-    </row>
-    <row r="209" spans="1:20">
+      <c r="U208">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="209" spans="1:21">
       <c r="A209" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B209" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C209" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D209" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E209" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="F209">
         <v>1675</v>
@@ -17037,22 +17667,25 @@
       <c r="T209">
         <v>2040</v>
       </c>
-    </row>
-    <row r="210" spans="1:20">
+      <c r="U209">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="210" spans="1:21">
       <c r="A210" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B210" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C210" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D210" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E210" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="F210">
         <v>39314</v>
@@ -17099,22 +17732,25 @@
       <c r="T210">
         <v>68153</v>
       </c>
-    </row>
-    <row r="211" spans="1:20">
+      <c r="U210">
+        <v>62318</v>
+      </c>
+    </row>
+    <row r="211" spans="1:21">
       <c r="A211" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B211" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C211" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D211" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E211" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F211">
         <v>4592</v>
@@ -17161,22 +17797,25 @@
       <c r="T211">
         <v>4975</v>
       </c>
-    </row>
-    <row r="212" spans="1:20">
+      <c r="U211">
+        <v>4641</v>
+      </c>
+    </row>
+    <row r="212" spans="1:21">
       <c r="A212" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B212" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C212" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D212" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E212" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="F212">
         <v>669</v>
@@ -17223,22 +17862,25 @@
       <c r="T212">
         <v>3029</v>
       </c>
-    </row>
-    <row r="213" spans="1:20">
+      <c r="U212">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="213" spans="1:21">
       <c r="A213" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B213" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C213" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D213" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E213" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="F213">
         <v>5058</v>
@@ -17285,22 +17927,25 @@
       <c r="T213">
         <v>8451</v>
       </c>
-    </row>
-    <row r="214" spans="1:20">
+      <c r="U213">
+        <v>7680</v>
+      </c>
+    </row>
+    <row r="214" spans="1:21">
       <c r="A214" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B214" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C214" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D214" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E214" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="F214">
         <v>3735</v>
@@ -17347,22 +17992,25 @@
       <c r="T214">
         <v>5849</v>
       </c>
-    </row>
-    <row r="215" spans="1:20">
+      <c r="U214">
+        <v>5487</v>
+      </c>
+    </row>
+    <row r="215" spans="1:21">
       <c r="A215" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B215" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C215" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D215" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E215" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="F215">
         <v>1776</v>
@@ -17409,22 +18057,25 @@
       <c r="T215">
         <v>2430</v>
       </c>
-    </row>
-    <row r="216" spans="1:20">
+      <c r="U215">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="216" spans="1:21">
       <c r="A216" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B216" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C216" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D216" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E216" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="F216">
         <v>6071</v>
@@ -17471,22 +18122,25 @@
       <c r="T216">
         <v>6863</v>
       </c>
-    </row>
-    <row r="217" spans="1:20">
+      <c r="U216">
+        <v>6748</v>
+      </c>
+    </row>
+    <row r="217" spans="1:21">
       <c r="A217" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B217" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C217" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D217" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E217" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="F217">
         <v>6131</v>
@@ -17533,22 +18187,25 @@
       <c r="T217">
         <v>10508</v>
       </c>
-    </row>
-    <row r="218" spans="1:20">
+      <c r="U217">
+        <v>9035</v>
+      </c>
+    </row>
+    <row r="218" spans="1:21">
       <c r="A218" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B218" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C218" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D218" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E218" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="F218">
         <v>3346</v>
@@ -17595,22 +18252,25 @@
       <c r="T218">
         <v>2445</v>
       </c>
-    </row>
-    <row r="219" spans="1:20">
+      <c r="U218">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="219" spans="1:21">
       <c r="A219" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B219" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C219" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D219" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E219" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="F219">
         <v>1229</v>
@@ -17657,22 +18317,25 @@
       <c r="T219">
         <v>6407</v>
       </c>
-    </row>
-    <row r="220" spans="1:20">
+      <c r="U219">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="220" spans="1:21">
       <c r="A220" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B220" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C220" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D220" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E220" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="F220">
         <v>3385</v>
@@ -17719,22 +18382,25 @@
       <c r="T220">
         <v>5531</v>
       </c>
-    </row>
-    <row r="221" spans="1:20">
+      <c r="U220">
+        <v>5365</v>
+      </c>
+    </row>
+    <row r="221" spans="1:21">
       <c r="A221" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B221" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C221" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D221" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E221" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -17781,22 +18447,25 @@
       <c r="T221">
         <v>5499</v>
       </c>
-    </row>
-    <row r="222" spans="1:20">
+      <c r="U221">
+        <v>5553</v>
+      </c>
+    </row>
+    <row r="222" spans="1:21">
       <c r="A222" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B222" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C222" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D222" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E222" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="F222">
         <v>3322</v>
@@ -17842,6 +18511,9 @@
       </c>
       <c r="T222">
         <v>6166</v>
+      </c>
+      <c r="U222">
+        <v>5670</v>
       </c>
     </row>
   </sheetData>
@@ -17856,418 +18528,418 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B2" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C2" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D2" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="E2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="F2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="G2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="H2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B3" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="C3" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="D3" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="E3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="F3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="G3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="H3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B4" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="C4" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D4" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="E4" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="F4" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="G4" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="H4" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="B5" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C5" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D5" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="E5" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F5" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="G5" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="H5" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B6" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C6" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D6" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="E6" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F6" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="G6" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="H6" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B7" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="C7" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D7" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="E7" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="F7" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="G7" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="H7" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B8" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C8" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D8" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="E8" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="F8" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="G8" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="H8" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B9" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="C9" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="D9" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="E9" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="F9" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="G9" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="H9" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B10" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C10" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D10" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E10" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="G10" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="H10" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B11" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="C11" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D11" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E11" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="F11" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="G11" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="H11" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="B12" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C12" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D12" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="E12" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="G12" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="H12" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B13" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="C13" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D13" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="E13" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="G13" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="H13" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B14" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="C14" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D14" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E14" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="F14" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="G14" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="H14" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B15" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C15" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="D15" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="E15" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="F15" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="G15" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="H15" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B16" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C16" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D16" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E16" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="F16" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="G16" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="H16" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
   </sheetData>
